--- a/PRUEBA4.xlsx
+++ b/PRUEBA4.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="8.28515625" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -460,6 +460,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,6 +486,9 @@
       <c r="F1" s="9" t="n">
         <v>46113</v>
       </c>
+      <c r="G1" s="9" t="n">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="n">
@@ -515,6 +519,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="1" t="n">
@@ -545,6 +554,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n">
@@ -575,6 +589,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n">
@@ -605,6 +624,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="1" t="n">
@@ -635,6 +659,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -657,6 +686,9 @@
       <c r="F7" s="8" t="n">
         <v>638433.2006637501</v>
       </c>
+      <c r="G7" s="8" t="n">
+        <v>657586.1966836626</v>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="1" t="n">
@@ -687,6 +719,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -709,6 +746,9 @@
       <c r="F9" s="8" t="n">
         <v>1122798.387671875</v>
       </c>
+      <c r="G9" s="8" t="n">
+        <v>1156482.339302031</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -731,6 +771,9 @@
       <c r="F10" s="8" t="n">
         <v>638433.2006637501</v>
       </c>
+      <c r="G10" s="8" t="n">
+        <v>657586.1966836626</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -753,6 +796,9 @@
       <c r="F11" s="8" t="n">
         <v>2064803.54445</v>
       </c>
+      <c r="G11" s="8" t="n">
+        <v>2126747.6507835</v>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="1" t="n">
@@ -783,6 +829,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -813,6 +864,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="1" t="n">
@@ -843,6 +899,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -865,6 +926,9 @@
       <c r="F15" s="8" t="n">
         <v>4103251.917770625</v>
       </c>
+      <c r="G15" s="8" t="n">
+        <v>4226349.475303744</v>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="1" t="n">
@@ -895,6 +959,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -917,6 +986,9 @@
       <c r="F17" s="8" t="n">
         <v>7022086.261963751</v>
       </c>
+      <c r="G17" s="8" t="n">
+        <v>7232748.849822664</v>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="1" t="n">
@@ -947,6 +1019,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -969,6 +1046,9 @@
       <c r="F19" s="8" t="n">
         <v>3517073.05531375</v>
       </c>
+      <c r="G19" s="8" t="n">
+        <v>3622585.246973163</v>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="1" t="n">
@@ -999,6 +1079,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="1" t="n">
@@ -1029,6 +1114,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1051,6 +1141,9 @@
       <c r="F22" s="8" t="n">
         <v>873071.066354375</v>
       </c>
+      <c r="G22" s="8" t="n">
+        <v>899263.1983450062</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1073,6 +1166,9 @@
       <c r="F23" s="8" t="n">
         <v>763937.17186375</v>
       </c>
+      <c r="G23" s="8" t="n">
+        <v>786855.2870196624</v>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="1" t="n">
@@ -1103,6 +1199,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1125,6 +1226,9 @@
       <c r="F25" s="8" t="n">
         <v>8474316.00347</v>
       </c>
+      <c r="G25" s="8" t="n">
+        <v>8728545.4835741</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1147,6 +1251,9 @@
       <c r="F26" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G26" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1169,6 +1276,9 @@
       <c r="F27" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G27" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1191,6 +1301,9 @@
       <c r="F28" s="8" t="n">
         <v>68208.68778875</v>
       </c>
+      <c r="G28" s="8" t="n">
+        <v>70254.9484224125</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1213,6 +1326,9 @@
       <c r="F29" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G29" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1235,6 +1351,9 @@
       <c r="F30" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G30" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1257,6 +1376,9 @@
       <c r="F31" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G31" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1279,6 +1401,9 @@
       <c r="F32" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G32" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1301,6 +1426,9 @@
       <c r="F33" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G33" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1323,6 +1451,9 @@
       <c r="F34" s="8" t="n">
         <v>193920.2836975</v>
       </c>
+      <c r="G34" s="8" t="n">
+        <v>199737.892208425</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1345,6 +1476,9 @@
       <c r="F35" s="8" t="n">
         <v>290880.42554625</v>
       </c>
+      <c r="G35" s="8" t="n">
+        <v>299606.8383126375</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1367,6 +1501,9 @@
       <c r="F36" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G36" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1389,6 +1526,9 @@
       <c r="F37" s="8" t="n">
         <v>213312.294153125</v>
       </c>
+      <c r="G37" s="8" t="n">
+        <v>219711.6629777187</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1411,6 +1551,9 @@
       <c r="F38" s="8" t="n">
         <v>242400.354621875</v>
       </c>
+      <c r="G38" s="8" t="n">
+        <v>249672.3652605313</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1433,6 +1576,9 @@
       <c r="F39" s="8" t="n">
         <v>121200.22209625</v>
       </c>
+      <c r="G39" s="8" t="n">
+        <v>124836.2287591375</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1455,6 +1601,9 @@
       <c r="F40" s="8" t="n">
         <v>184224.26354125</v>
       </c>
+      <c r="G40" s="8" t="n">
+        <v>189750.9914474875</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1477,6 +1626,9 @@
       <c r="F41" s="8" t="n">
         <v>81446.50959875001</v>
       </c>
+      <c r="G41" s="8" t="n">
+        <v>83889.90488671251</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1499,6 +1651,9 @@
       <c r="F42" s="8" t="n">
         <v>271488.38523375</v>
       </c>
+      <c r="G42" s="8" t="n">
+        <v>279633.0367907625</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1521,6 +1676,9 @@
       <c r="F43" s="8" t="n">
         <v>135922.975584375</v>
       </c>
+      <c r="G43" s="8" t="n">
+        <v>140000.6648519062</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1543,6 +1701,9 @@
       <c r="F44" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G44" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1565,6 +1726,9 @@
       <c r="F45" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G45" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1586,6 +1750,9 @@
       </c>
       <c r="F46" s="8" t="n">
         <v>60023.634505625</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>61824.34354079375</v>
       </c>
     </row>
   </sheetData>
